--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BALONCESTO ALCALA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BALONCESTO ALCALA.xlsx
@@ -565,13 +565,13 @@
         <v>20</v>
       </c>
       <c r="D2" t="n">
-        <v>72.7743</v>
+        <v>58.3343</v>
       </c>
       <c r="E2" t="n">
-        <v>53.7976</v>
+        <v>49.592</v>
       </c>
       <c r="F2" t="n">
-        <v>18.9766</v>
+        <v>8.742599999999999</v>
       </c>
       <c r="G2" t="n">
         <v>0.2963999999999998</v>
@@ -610,13 +610,13 @@
         <v>46.918</v>
       </c>
       <c r="S2" t="n">
-        <v>28.4512</v>
+        <v>14.0116</v>
       </c>
       <c r="T2" t="n">
-        <v>8.3447</v>
+        <v>4.1389</v>
       </c>
       <c r="U2" t="n">
-        <v>20.1065</v>
+        <v>9.8726</v>
       </c>
       <c r="V2" t="n">
         <v>51.3635</v>
@@ -643,13 +643,13 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>8.8245</v>
+        <v>12.0488</v>
       </c>
       <c r="E3" t="n">
-        <v>7.537700000000001</v>
+        <v>9.7165</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2869</v>
+        <v>2.3325</v>
       </c>
       <c r="G3" t="n">
         <v>7.7275</v>
@@ -688,13 +688,13 @@
         <v>7.530100000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2249</v>
+        <v>1.9994</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8014999999999999</v>
+        <v>1.3773</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4235</v>
+        <v>0.6222000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0.005099999999999938</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. MARTINEZ SERNA</t>
+          <t>J. JIMENEZ LAHOZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9712</v>
+        <v>6.817</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2239</v>
+        <v>20.0241</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7473000000000001</v>
+        <v>-13.2071</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0485</v>
+        <v>1.770800000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1299</v>
+        <v>2.364199999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9184</v>
+        <v>-0.5936999999999997</v>
       </c>
       <c r="J4" t="n">
-        <v>5.693099999999999</v>
+        <v>33.7813</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3041</v>
+        <v>25.3446</v>
       </c>
       <c r="L4" t="n">
-        <v>3.389</v>
+        <v>8.4367</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6447</v>
+        <v>-32.0105</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1742</v>
+        <v>-22.9799</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4702999999999999</v>
+        <v>-9.0304</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3860999999999999</v>
+        <v>7.916399999999999</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.0547</v>
+        <v>-29.7344</v>
       </c>
       <c r="R4" t="n">
-        <v>3.6685</v>
+        <v>37.65</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3681</v>
+        <v>0.5428000000000004</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4146</v>
+        <v>0.7841</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9534</v>
+        <v>-0.2412000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3231000000000001</v>
+        <v>-3.4127</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>15.1925</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3231000000000001</v>
+        <v>-18.6055</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MARTÍNEZ BRUNO</t>
+          <t>D. MARTINEZ SERNA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2655999999999998</v>
+        <v>3.553</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.3345</v>
+        <v>2.3201</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6002</v>
+        <v>1.2329</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.8289</v>
+        <v>4.0485</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.2811</v>
+        <v>1.1299</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.5479</v>
+        <v>2.9184</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2333000000000007</v>
+        <v>5.693099999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3091</v>
+        <v>2.3041</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.0756</v>
+        <v>3.389</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.0623</v>
+        <v>-1.6447</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.5901</v>
+        <v>-1.1742</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4721</v>
+        <v>-0.4702999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>4.054600000000001</v>
+        <v>-0.3860999999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-8.4956</v>
+        <v>-4.0547</v>
       </c>
       <c r="R5" t="n">
-        <v>12.5502</v>
+        <v>3.6685</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1618</v>
+        <v>0.2138</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1407999999999999</v>
+        <v>0.6817</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3027</v>
+        <v>-0.4679</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1219</v>
+        <v>-0.3231000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>5.0685</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.1904</v>
+        <v>-0.3231000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2006</v>
+        <v>0.7590999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8797</v>
+        <v>-0.9831000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0801</v>
+        <v>1.7422</v>
       </c>
       <c r="G6" t="n">
         <v>-0.5147999999999999</v>
@@ -922,13 +922,13 @@
         <v>1.3516</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2205</v>
+        <v>0.7792</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7443</v>
+        <v>0.6407</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5237000000000001</v>
+        <v>0.1385</v>
       </c>
       <c r="V6" t="n">
         <v>-0.8568</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. ELTING</t>
+          <t>J. MARTÍNEZ BRUNO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1050999999999997</v>
+        <v>0.2132999999999998</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7444999999999999</v>
+        <v>-3.9273</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8495</v>
+        <v>4.140700000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01149999999999994</v>
+        <v>-4.8289</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0958</v>
+        <v>-2.2811</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0843</v>
+        <v>-2.5479</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1441</v>
+        <v>0.2333000000000007</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4417</v>
+        <v>1.3091</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2976</v>
+        <v>-1.0756</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1326</v>
+        <v>-5.0623</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3459</v>
+        <v>-3.5901</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7867</v>
+        <v>-1.4721</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7723</v>
+        <v>4.054600000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.317</v>
+        <v>-8.4956</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5447</v>
+        <v>12.5502</v>
       </c>
       <c r="S7" t="n">
-        <v>0.866</v>
+        <v>2.1096</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7992</v>
+        <v>-0.7337</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0669</v>
+        <v>2.8432</v>
       </c>
       <c r="V7" t="n">
-        <v>5.551115123125783e-17</v>
+        <v>-1.1219</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3709</v>
+        <v>5.0685</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3709</v>
+        <v>-6.1904</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ SANCHEZ</t>
+          <t>B. ELTING</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2621</v>
+        <v>0.1562000000000003</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0552</v>
+        <v>-0.7927</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2069</v>
+        <v>0.9489</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2069</v>
+        <v>0.01149999999999994</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2069</v>
+        <v>2.0958</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-2.0843</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.1441</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2.4417</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.2976</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2069</v>
+        <v>-1.1326</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2069</v>
+        <v>-0.3459</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.7867</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.317</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5447</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0552</v>
+        <v>0.917</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0552</v>
+        <v>0.7509</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.1661</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.3709</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. SASTRE DIAZ</t>
+          <t>S. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,61 +1108,61 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3239</v>
+        <v>-0.2621</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0971</v>
+        <v>-0.0552</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2267</v>
+        <v>-0.2069</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2263</v>
+        <v>-0.2069</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1721</v>
+        <v>-0.2069</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0542</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1442</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1035</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0407</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.08210000000000001</v>
+        <v>-0.2069</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06860000000000001</v>
+        <v>-0.2069</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0135</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9708</v>
+        <v>-0.0552</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2759</v>
+        <v>-0.0552</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6949000000000001</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. VALVERDE SASTRE</t>
+          <t>R. SASTRE DIAZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3162</v>
+        <v>-0.7115</v>
       </c>
       <c r="E10" t="n">
-        <v>8.8719</v>
+        <v>-0.6835</v>
       </c>
       <c r="F10" t="n">
-        <v>-11.1881</v>
+        <v>-0.02809999999999996</v>
       </c>
       <c r="G10" t="n">
-        <v>-23.4887</v>
+        <v>0.2263</v>
       </c>
       <c r="H10" t="n">
-        <v>-25.3733</v>
+        <v>0.1721</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8845</v>
+        <v>0.0542</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9786000000000011</v>
+        <v>0.1442</v>
       </c>
       <c r="K10" t="n">
-        <v>-4.603</v>
+        <v>0.1035</v>
       </c>
       <c r="L10" t="n">
-        <v>5.582</v>
+        <v>0.0407</v>
       </c>
       <c r="M10" t="n">
-        <v>-24.4674</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-20.7702</v>
+        <v>0.06860000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.6973</v>
+        <v>0.0135</v>
       </c>
       <c r="P10" t="n">
-        <v>7.9163</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q10" t="n">
-        <v>-19.6942</v>
+        <v>-0.9654</v>
       </c>
       <c r="R10" t="n">
-        <v>27.61</v>
+        <v>0.3862</v>
       </c>
       <c r="S10" t="n">
-        <v>22.0958</v>
+        <v>-0.3585</v>
       </c>
       <c r="T10" t="n">
-        <v>20.3192</v>
+        <v>0.1377</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7768</v>
+        <v>-0.4962</v>
       </c>
       <c r="V10" t="n">
-        <v>-8.8393</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>7.2679</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-16.1075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. LOPEZ SANCHEZ</t>
+          <t>D. AVILA MERCADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5629</v>
+        <v>-1.880000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0551</v>
+        <v>5.197800000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5078</v>
+        <v>-7.0778</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0483</v>
+        <v>3.9209</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1862</v>
+        <v>0.4398999999999997</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1379</v>
+        <v>3.4808</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0207</v>
+        <v>40.449</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0207</v>
+        <v>24.0405</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>16.4085</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-36.5282</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2069</v>
+        <v>-23.6004</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1379</v>
+        <v>-12.9278</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9654</v>
+        <v>-13.3225</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9654</v>
+        <v>-45.9529</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>32.6301</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.09379999999999999</v>
+        <v>3.7575</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1104</v>
+        <v>-0.2499999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0166</v>
+        <v>4.0072</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4554</v>
+        <v>3.7641</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>10.9511</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4554</v>
+        <v>-7.1871</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>M. LOPEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6121</v>
+        <v>-3.4829</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.2423</v>
+        <v>-0.9999</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.37</v>
+        <v>-2.483</v>
       </c>
       <c r="G12" t="n">
-        <v>-25.4557</v>
+        <v>-0.0483</v>
       </c>
       <c r="H12" t="n">
-        <v>-21.4759</v>
+        <v>-0.1862</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.9799</v>
+        <v>0.1379</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0899</v>
+        <v>0.0207</v>
       </c>
       <c r="K12" t="n">
-        <v>-8.498200000000001</v>
+        <v>0.0207</v>
       </c>
       <c r="L12" t="n">
-        <v>7.408700000000001</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-24.3657</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>-12.9775</v>
+        <v>-0.2069</v>
       </c>
       <c r="O12" t="n">
-        <v>-11.3881</v>
+        <v>0.1379</v>
       </c>
       <c r="P12" t="n">
-        <v>20.6592</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q12" t="n">
-        <v>-11.1987</v>
+        <v>-0.9654</v>
       </c>
       <c r="R12" t="n">
-        <v>31.8579</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>10.3586</v>
+        <v>-0.0138</v>
       </c>
       <c r="T12" t="n">
-        <v>7.163</v>
+        <v>-0.0552</v>
       </c>
       <c r="U12" t="n">
-        <v>3.1958</v>
+        <v>0.0414</v>
       </c>
       <c r="V12" t="n">
-        <v>-9.1744</v>
+        <v>-2.4554</v>
       </c>
       <c r="W12" t="n">
-        <v>3.8834</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-13.0578</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. JIMENEZ LAHOZ</t>
+          <t>D. MARTINEZ DE LA SERNA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.512999999999999</v>
+        <v>-6.2502</v>
       </c>
       <c r="E13" t="n">
-        <v>14.5701</v>
+        <v>-11.2815</v>
       </c>
       <c r="F13" t="n">
-        <v>-19.0831</v>
+        <v>5.031000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>1.770800000000001</v>
+        <v>2.9286</v>
       </c>
       <c r="H13" t="n">
-        <v>2.364199999999999</v>
+        <v>-4.375500000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5936999999999997</v>
+        <v>7.303999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>33.7813</v>
+        <v>6.302899999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>25.3446</v>
+        <v>0.6646000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>8.4367</v>
+        <v>5.638500000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-32.0105</v>
+        <v>-3.3744</v>
       </c>
       <c r="N13" t="n">
-        <v>-22.9799</v>
+        <v>-5.039899999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.0304</v>
+        <v>1.6658</v>
       </c>
       <c r="P13" t="n">
-        <v>7.916399999999999</v>
+        <v>-3.0892</v>
       </c>
       <c r="Q13" t="n">
-        <v>-29.7344</v>
+        <v>-19.1149</v>
       </c>
       <c r="R13" t="n">
-        <v>37.65</v>
+        <v>16.0257</v>
       </c>
       <c r="S13" t="n">
-        <v>-10.7874</v>
+        <v>-0.242</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.6698</v>
+        <v>-1.9821</v>
       </c>
       <c r="U13" t="n">
-        <v>-6.1174</v>
+        <v>1.7401</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.4127</v>
+        <v>-5.8477</v>
       </c>
       <c r="W13" t="n">
-        <v>15.1925</v>
+        <v>3.5126</v>
       </c>
       <c r="X13" t="n">
-        <v>-18.6055</v>
+        <v>-9.360300000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MARTÍNEZ LAGO</t>
+          <t>M. YOUNG MEDIERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.0368</v>
+        <v>-8.216199999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.964299999999999</v>
+        <v>-3.567</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.071900000000001</v>
+        <v>-4.6492</v>
       </c>
       <c r="G14" t="n">
-        <v>-27.9863</v>
+        <v>-5.4472</v>
       </c>
       <c r="H14" t="n">
-        <v>-23.4169</v>
+        <v>-3.4583</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.5693</v>
+        <v>-1.988699999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3163999999999997</v>
+        <v>15.4263</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.5419</v>
+        <v>10.2072</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2259</v>
+        <v>5.2191</v>
       </c>
       <c r="M14" t="n">
-        <v>-27.6701</v>
+        <v>-20.8734</v>
       </c>
       <c r="N14" t="n">
-        <v>-21.8745</v>
+        <v>-13.6655</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.795</v>
+        <v>-7.208</v>
       </c>
       <c r="P14" t="n">
-        <v>9.8469</v>
+        <v>2.703</v>
       </c>
       <c r="Q14" t="n">
-        <v>-22.0113</v>
+        <v>-23.5558</v>
       </c>
       <c r="R14" t="n">
-        <v>31.8576</v>
+        <v>26.2585</v>
       </c>
       <c r="S14" t="n">
-        <v>26.3507</v>
+        <v>-0.05569999999999981</v>
       </c>
       <c r="T14" t="n">
-        <v>19.5459</v>
+        <v>-1.6063</v>
       </c>
       <c r="U14" t="n">
-        <v>6.8047</v>
+        <v>1.5504</v>
       </c>
       <c r="V14" t="n">
-        <v>-13.2477</v>
+        <v>-5.4163</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.1830999999999997</v>
+        <v>6.1684</v>
       </c>
       <c r="X14" t="n">
-        <v>-13.0646</v>
+        <v>-11.5847</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. AVILA MERCADO</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>19</v>
       </c>
       <c r="D15" t="n">
-        <v>-6.415999999999999</v>
+        <v>-8.834599999999998</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4399</v>
+        <v>-6.7371</v>
       </c>
       <c r="F15" t="n">
-        <v>-7.8555</v>
+        <v>-2.0975</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9209</v>
+        <v>-25.4557</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4398999999999997</v>
+        <v>-21.4759</v>
       </c>
       <c r="I15" t="n">
-        <v>3.4808</v>
+        <v>-3.9799</v>
       </c>
       <c r="J15" t="n">
-        <v>40.449</v>
+        <v>-1.0899</v>
       </c>
       <c r="K15" t="n">
-        <v>24.0405</v>
+        <v>-8.498200000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>16.4085</v>
+        <v>7.408700000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-36.5282</v>
+        <v>-24.3657</v>
       </c>
       <c r="N15" t="n">
-        <v>-23.6004</v>
+        <v>-12.9775</v>
       </c>
       <c r="O15" t="n">
-        <v>-12.9278</v>
+        <v>-11.3881</v>
       </c>
       <c r="P15" t="n">
-        <v>-13.3225</v>
+        <v>20.6592</v>
       </c>
       <c r="Q15" t="n">
-        <v>-45.9529</v>
+        <v>-11.1987</v>
       </c>
       <c r="R15" t="n">
-        <v>32.6301</v>
+        <v>31.8579</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7779000000000004</v>
+        <v>5.1362</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.007900000000001</v>
+        <v>1.668</v>
       </c>
       <c r="U15" t="n">
-        <v>3.2297</v>
+        <v>3.4685</v>
       </c>
       <c r="V15" t="n">
-        <v>3.7641</v>
+        <v>-9.1744</v>
       </c>
       <c r="W15" t="n">
-        <v>10.9511</v>
+        <v>3.8834</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.1871</v>
+        <v>-13.0578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. MARTINEZ DE LA SERNA</t>
+          <t>J. BECERRA ORDOÑEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="D16" t="n">
-        <v>-11.6969</v>
+        <v>-11.579</v>
       </c>
       <c r="E16" t="n">
-        <v>-14.405</v>
+        <v>-2.860299999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>2.7081</v>
+        <v>-8.7189</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9286</v>
+        <v>-4.8028</v>
       </c>
       <c r="H16" t="n">
-        <v>-4.375500000000001</v>
+        <v>0.008199999999999541</v>
       </c>
       <c r="I16" t="n">
-        <v>7.303999999999999</v>
+        <v>-4.811100000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>6.302899999999999</v>
+        <v>12.6131</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6646000000000001</v>
+        <v>9.604100000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>5.638500000000001</v>
+        <v>3.0096</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.3744</v>
+        <v>-17.4162</v>
       </c>
       <c r="N16" t="n">
-        <v>-5.039899999999999</v>
+        <v>-9.5959</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6658</v>
+        <v>-7.820600000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.0892</v>
+        <v>-1.9309</v>
       </c>
       <c r="Q16" t="n">
-        <v>-19.1149</v>
+        <v>-30.8928</v>
       </c>
       <c r="R16" t="n">
-        <v>16.0257</v>
+        <v>28.9614</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.6887</v>
+        <v>3.495</v>
       </c>
       <c r="T16" t="n">
-        <v>-5.1056</v>
+        <v>4.097</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5829999999999999</v>
+        <v>-0.6019000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-5.8477</v>
+        <v>-8.3406</v>
       </c>
       <c r="W16" t="n">
-        <v>3.5126</v>
+        <v>11.322</v>
       </c>
       <c r="X16" t="n">
-        <v>-9.360300000000001</v>
+        <v>-19.6625</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. YOUNG MEDIERO</t>
+          <t>J. VALVERDE SASTRE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D17" t="n">
-        <v>-13.0646</v>
+        <v>-14.6837</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.676600000000001</v>
+        <v>-4.745</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.3883</v>
+        <v>-9.938700000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.4472</v>
+        <v>-23.4887</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.4583</v>
+        <v>-25.3733</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.988699999999999</v>
+        <v>1.8845</v>
       </c>
       <c r="J17" t="n">
-        <v>15.4263</v>
+        <v>0.9786000000000011</v>
       </c>
       <c r="K17" t="n">
-        <v>10.2072</v>
+        <v>-4.603</v>
       </c>
       <c r="L17" t="n">
-        <v>5.2191</v>
+        <v>5.582</v>
       </c>
       <c r="M17" t="n">
-        <v>-20.8734</v>
+        <v>-24.4674</v>
       </c>
       <c r="N17" t="n">
-        <v>-13.6655</v>
+        <v>-20.7702</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.208</v>
+        <v>-3.6973</v>
       </c>
       <c r="P17" t="n">
-        <v>2.703</v>
+        <v>7.9163</v>
       </c>
       <c r="Q17" t="n">
-        <v>-23.5558</v>
+        <v>-19.6942</v>
       </c>
       <c r="R17" t="n">
-        <v>26.2585</v>
+        <v>27.61</v>
       </c>
       <c r="S17" t="n">
-        <v>-4.9042</v>
+        <v>9.728300000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-5.7155</v>
+        <v>6.7021</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8113000000000002</v>
+        <v>3.0261</v>
       </c>
       <c r="V17" t="n">
-        <v>-5.4163</v>
+        <v>-8.8393</v>
       </c>
       <c r="W17" t="n">
-        <v>6.1684</v>
+        <v>7.2679</v>
       </c>
       <c r="X17" t="n">
-        <v>-11.5847</v>
+        <v>-16.1075</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. BECERRA ORDOÑEZ</t>
+          <t>A. MARTÍNEZ LAGO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>-13.9728</v>
+        <v>-18.4452</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.1018</v>
+        <v>-14.3474</v>
       </c>
       <c r="F18" t="n">
-        <v>-10.871</v>
+        <v>-4.097399999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.8028</v>
+        <v>-27.9863</v>
       </c>
       <c r="H18" t="n">
-        <v>0.008199999999999541</v>
+        <v>-23.4169</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.811100000000001</v>
+        <v>-4.5693</v>
       </c>
       <c r="J18" t="n">
-        <v>12.6131</v>
+        <v>-0.3163999999999997</v>
       </c>
       <c r="K18" t="n">
-        <v>9.604100000000001</v>
+        <v>-1.5419</v>
       </c>
       <c r="L18" t="n">
-        <v>3.0096</v>
+        <v>1.2259</v>
       </c>
       <c r="M18" t="n">
-        <v>-17.4162</v>
+        <v>-27.6701</v>
       </c>
       <c r="N18" t="n">
-        <v>-9.5959</v>
+        <v>-21.8745</v>
       </c>
       <c r="O18" t="n">
-        <v>-7.820600000000001</v>
+        <v>-5.795</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.9309</v>
+        <v>9.8469</v>
       </c>
       <c r="Q18" t="n">
-        <v>-30.8928</v>
+        <v>-22.0113</v>
       </c>
       <c r="R18" t="n">
-        <v>28.9614</v>
+        <v>31.8576</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1012</v>
+        <v>12.942</v>
       </c>
       <c r="T18" t="n">
-        <v>3.855399999999999</v>
+        <v>8.1631</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.7537</v>
+        <v>4.779</v>
       </c>
       <c r="V18" t="n">
-        <v>-8.3406</v>
+        <v>-13.2477</v>
       </c>
       <c r="W18" t="n">
-        <v>11.322</v>
+        <v>-0.1830999999999997</v>
       </c>
       <c r="X18" t="n">
-        <v>-19.6625</v>
+        <v>-13.0646</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>-32.8588</v>
+        <v>-21.1432</v>
       </c>
       <c r="E19" t="n">
-        <v>-21.1232</v>
+        <v>-13.2838</v>
       </c>
       <c r="F19" t="n">
-        <v>-11.7353</v>
+        <v>-7.8595</v>
       </c>
       <c r="G19" t="n">
         <v>-18.107</v>
@@ -1936,13 +1936,13 @@
         <v>30.1202</v>
       </c>
       <c r="S19" t="n">
-        <v>-9.324</v>
+        <v>2.3916</v>
       </c>
       <c r="T19" t="n">
-        <v>-7.3981</v>
+        <v>0.4413000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.9262</v>
+        <v>1.95</v>
       </c>
       <c r="V19" t="n">
         <v>-9.868300000000001</v>
@@ -1969,13 +1969,13 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-48.4003</v>
+        <v>-29.9799</v>
       </c>
       <c r="E20" t="n">
-        <v>-30.3768</v>
+        <v>-16.3041</v>
       </c>
       <c r="F20" t="n">
-        <v>-18.0236</v>
+        <v>-13.6757</v>
       </c>
       <c r="G20" t="n">
         <v>-37.675</v>
@@ -2014,13 +2014,13 @@
         <v>43.4425</v>
       </c>
       <c r="S20" t="n">
-        <v>-17.532</v>
+        <v>0.8884000000000004</v>
       </c>
       <c r="T20" t="n">
-        <v>-17.6896</v>
+        <v>-3.6171</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1577000000000001</v>
+        <v>4.5052</v>
       </c>
       <c r="V20" t="n">
         <v>4.8759</v>
@@ -2047,13 +2047,13 @@
         <v>26</v>
       </c>
       <c r="D21" t="n">
-        <v>-62.8951</v>
+        <v>-43.58680000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6149999999999807</v>
+        <v>6.282600000000002</v>
       </c>
       <c r="F21" t="n">
-        <v>-62.2795</v>
+        <v>-49.86899999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-127.6311</v>
@@ -2092,16 +2092,16 @@
         <v>380.3632</v>
       </c>
       <c r="S21" t="n">
-        <v>38.87880000000001</v>
+        <v>58.1872</v>
       </c>
       <c r="T21" t="n">
-        <v>14.38679999999999</v>
+        <v>21.2832</v>
       </c>
       <c r="U21" t="n">
-        <v>24.4929</v>
+        <v>36.9033</v>
       </c>
       <c r="V21" t="n">
-        <v>-8.895599999999998</v>
+        <v>-8.895600000000005</v>
       </c>
       <c r="W21" t="n">
         <v>156.3642</v>
